--- a/SeleniumTests/TestDataFolder/LogAllTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/LogAllTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0F064C-9BD6-46C5-B25B-BC2B1EBDD019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23B20FA-B015-479B-AE64-6486741F3041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31380" yWindow="2100" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SearchLogTestData" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
-    <t>searchText</t>
-  </si>
-  <si>
-    <t>columnIndex</t>
-  </si>
-  <si>
     <t>yanshen.choo@qubeapps.com</t>
   </si>
   <si>
@@ -44,10 +38,16 @@
     <t>Yan Shen</t>
   </si>
   <si>
-    <t>User</t>
-  </si>
-  <si>
     <t>Setting</t>
+  </si>
+  <si>
+    <t>Search Text</t>
+  </si>
+  <si>
+    <t>Refer Column Index</t>
+  </si>
+  <si>
+    <t>User Name Filter</t>
   </si>
 </sst>
 </file>
@@ -380,20 +380,21 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -401,7 +402,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>3</v>
@@ -409,7 +410,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2">
         <v>4</v>
@@ -428,20 +429,21 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -460,20 +462,21 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
